--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5783" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5797" uniqueCount="444">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,6 +485,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -674,6 +677,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -684,10 +690,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -700,6 +721,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -707,6 +737,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -714,6 +747,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1302,6 +1338,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1678,7 +1720,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4099,7 +4141,9 @@
       <c r="K24" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4170,10 +4214,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4207,7 +4251,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -4229,7 +4273,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4247,7 +4291,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4267,10 +4311,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4304,7 +4348,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -4326,7 +4370,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4344,7 +4388,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4364,10 +4408,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4381,7 +4425,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4393,10 +4437,10 @@
         <v>95</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4447,7 +4491,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4467,10 +4511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4484,7 +4528,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4493,13 +4537,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4550,7 +4594,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4570,10 +4614,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4671,10 +4715,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4703,7 +4747,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4715,7 +4759,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4754,7 +4798,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4774,17 +4818,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
@@ -4806,7 +4850,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4818,7 +4862,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4857,7 +4901,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4877,17 +4921,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4909,7 +4953,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4921,7 +4965,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4960,7 +5004,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4980,17 +5024,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -5012,7 +5056,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5063,7 +5107,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5083,17 +5127,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>75</v>
@@ -5115,7 +5159,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5127,7 +5171,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -5166,7 +5210,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5186,10 +5230,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5212,11 +5256,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5267,7 +5311,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5287,10 +5331,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5317,7 +5361,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5368,7 +5412,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5388,17 +5432,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5416,11 +5460,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5471,7 +5515,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5491,17 +5535,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5519,11 +5563,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5574,7 +5618,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5594,17 +5638,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5622,11 +5666,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5677,7 +5721,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5697,10 +5741,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5723,16 +5767,18 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5780,7 +5826,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5800,10 +5846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5817,7 +5863,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5826,15 +5872,17 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -5883,7 +5931,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5903,10 +5951,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5929,12 +5977,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5982,7 +6034,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6002,10 +6054,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6030,10 +6082,14 @@
       <c r="K43" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L43" s="2"/>
+      <c r="L43" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>74</v>
       </c>
@@ -6061,7 +6117,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -6079,7 +6135,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6099,10 +6155,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6125,12 +6181,18 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
       </c>
@@ -6178,7 +6240,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6198,10 +6260,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6224,12 +6286,14 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -6277,7 +6341,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6297,10 +6361,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6323,12 +6387,14 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6376,7 +6442,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6396,10 +6462,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6413,7 +6479,7 @@
         <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6422,7 +6488,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6463,7 +6529,7 @@
         <v>74</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -6473,7 +6539,7 @@
         <v>124</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6493,13 +6559,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>74</v>
@@ -6521,7 +6587,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6574,7 +6640,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6594,10 +6660,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6695,10 +6761,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6796,10 +6862,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6897,10 +6963,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6998,10 +7064,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7101,10 +7167,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7204,10 +7270,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7307,10 +7373,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7410,10 +7476,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7511,10 +7577,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7544,7 +7610,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
@@ -7570,7 +7636,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7588,7 +7654,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7608,10 +7674,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7645,7 +7711,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>74</v>
@@ -7687,7 +7753,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7707,10 +7773,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7733,7 +7799,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7786,7 +7852,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7806,10 +7872,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7832,7 +7898,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7885,7 +7951,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7905,10 +7971,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7931,10 +7997,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -7986,7 +8052,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8006,10 +8072,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8032,7 +8098,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -8085,7 +8151,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8105,10 +8171,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8131,7 +8197,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -8184,7 +8250,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8204,10 +8270,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8230,7 +8296,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -8283,7 +8349,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8303,10 +8369,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8329,7 +8395,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8382,7 +8448,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8402,10 +8468,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8428,7 +8494,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8481,7 +8547,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8501,10 +8567,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8527,7 +8593,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8580,7 +8646,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8600,13 +8666,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
@@ -8628,7 +8694,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8681,7 +8747,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8701,10 +8767,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8802,10 +8868,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8903,10 +8969,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9004,10 +9070,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9105,10 +9171,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9208,10 +9274,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9311,10 +9377,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9414,10 +9480,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9517,10 +9583,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9618,10 +9684,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9651,7 +9717,7 @@
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
@@ -9677,7 +9743,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9695,7 +9761,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9715,10 +9781,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9752,7 +9818,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>74</v>
@@ -9794,7 +9860,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9814,10 +9880,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9840,7 +9906,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9893,7 +9959,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9913,10 +9979,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9939,7 +10005,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9992,7 +10058,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10012,10 +10078,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10038,7 +10104,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10091,7 +10157,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10111,10 +10177,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10137,7 +10203,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10190,7 +10256,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10210,10 +10276,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10236,7 +10302,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10289,7 +10355,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10309,10 +10375,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10335,10 +10401,10 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -10390,7 +10456,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10410,10 +10476,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10436,7 +10502,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10489,7 +10555,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10509,10 +10575,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10535,7 +10601,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10588,7 +10654,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10608,10 +10674,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10634,7 +10700,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10687,7 +10753,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10707,13 +10773,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>74</v>
@@ -10735,7 +10801,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10788,7 +10854,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10808,10 +10874,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10909,10 +10975,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11010,10 +11076,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11111,10 +11177,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11212,10 +11278,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11315,10 +11381,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11418,10 +11484,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11521,10 +11587,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11624,10 +11690,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11725,10 +11791,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11758,7 +11824,7 @@
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
@@ -11784,7 +11850,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>74</v>
@@ -11802,7 +11868,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11822,10 +11888,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11859,7 +11925,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>74</v>
@@ -11901,7 +11967,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11921,10 +11987,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11947,7 +12013,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12000,7 +12066,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12020,10 +12086,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12046,7 +12112,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12099,7 +12165,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12119,10 +12185,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12145,10 +12211,10 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -12200,7 +12266,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12220,10 +12286,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12246,7 +12312,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12299,7 +12365,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12319,10 +12385,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12345,7 +12411,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12398,7 +12464,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12418,10 +12484,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12444,7 +12510,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12497,7 +12563,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12517,10 +12583,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12543,7 +12609,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12596,7 +12662,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12616,10 +12682,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12642,7 +12708,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12695,7 +12761,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12715,10 +12781,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12741,7 +12807,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12794,7 +12860,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12814,13 +12880,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>74</v>
@@ -12842,7 +12908,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12895,7 +12961,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12915,10 +12981,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13016,10 +13082,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13117,10 +13183,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13218,10 +13284,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13319,10 +13385,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13422,10 +13488,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13525,10 +13591,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13628,10 +13694,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13731,10 +13797,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13832,10 +13898,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13865,7 +13931,7 @@
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
@@ -13891,7 +13957,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>74</v>
@@ -13909,7 +13975,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13929,10 +13995,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13966,7 +14032,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>74</v>
@@ -14008,7 +14074,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14028,10 +14094,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14054,7 +14120,7 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14107,7 +14173,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14127,10 +14193,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14153,7 +14219,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14206,7 +14272,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14226,10 +14292,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14252,10 +14318,10 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -14307,7 +14373,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14327,10 +14393,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14353,7 +14419,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14406,7 +14472,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14426,10 +14492,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14452,7 +14518,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14505,7 +14571,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14525,10 +14591,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14551,7 +14617,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -14604,7 +14670,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14624,10 +14690,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14650,7 +14716,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14703,7 +14769,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14723,10 +14789,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14749,7 +14815,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -14802,7 +14868,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14822,10 +14888,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14848,7 +14914,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -14901,7 +14967,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14921,13 +14987,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>74</v>
@@ -14949,7 +15015,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15002,7 +15068,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15022,10 +15088,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15123,10 +15189,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15224,10 +15290,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15325,10 +15391,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15426,10 +15492,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15529,10 +15595,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15632,10 +15698,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15735,10 +15801,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15838,10 +15904,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15939,10 +16005,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -15972,7 +16038,7 @@
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
@@ -15998,7 +16064,7 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>74</v>
@@ -16016,7 +16082,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16036,10 +16102,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16073,7 +16139,7 @@
       </c>
       <c r="Q143" s="2"/>
       <c r="R143" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S143" t="s" s="2">
         <v>74</v>
@@ -16115,7 +16181,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16135,10 +16201,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16161,7 +16227,7 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16214,7 +16280,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16234,10 +16300,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16260,7 +16326,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16313,7 +16379,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16333,10 +16399,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16359,10 +16425,10 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
@@ -16414,7 +16480,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16434,10 +16500,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16460,7 +16526,7 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16513,7 +16579,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16533,10 +16599,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16559,7 +16625,7 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -16612,7 +16678,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16632,10 +16698,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16658,7 +16724,7 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -16711,7 +16777,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -16731,10 +16797,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16757,7 +16823,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -16810,7 +16876,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -16830,10 +16896,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16856,7 +16922,7 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -16909,7 +16975,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -16929,10 +16995,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -16955,7 +17021,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17008,7 +17074,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17028,13 +17094,13 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="D153" t="s" s="2">
         <v>74</v>
@@ -17056,7 +17122,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17109,7 +17175,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17129,10 +17195,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17230,10 +17296,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17331,10 +17397,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17432,10 +17498,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17533,10 +17599,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17636,10 +17702,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17739,10 +17805,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17842,10 +17908,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -17945,10 +18011,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18046,10 +18112,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18079,7 +18145,7 @@
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
@@ -18105,7 +18171,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>74</v>
@@ -18123,7 +18189,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18143,10 +18209,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18180,7 +18246,7 @@
       </c>
       <c r="Q164" s="2"/>
       <c r="R164" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S164" t="s" s="2">
         <v>74</v>
@@ -18222,7 +18288,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18242,10 +18308,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18268,7 +18334,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18321,7 +18387,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18341,10 +18407,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18367,7 +18433,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -18420,7 +18486,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -18440,10 +18506,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18466,7 +18532,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -18519,7 +18585,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18539,10 +18605,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18565,7 +18631,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -18618,7 +18684,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -18638,10 +18704,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18664,7 +18730,7 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -18717,7 +18783,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -18737,10 +18803,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18763,7 +18829,7 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -18816,7 +18882,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -18836,10 +18902,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -18862,7 +18928,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -18915,7 +18981,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -18935,10 +19001,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -18961,10 +19027,10 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
@@ -19016,7 +19082,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -19036,10 +19102,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19062,7 +19128,7 @@
         <v>74</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19115,7 +19181,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -19135,10 +19201,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19161,12 +19227,16 @@
         <v>74</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="L174" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
+      <c r="O174" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>74</v>
       </c>
@@ -19214,7 +19284,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -19234,10 +19304,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19335,10 +19405,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19436,10 +19506,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19537,10 +19607,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19638,10 +19708,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -19741,10 +19811,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -19844,10 +19914,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -19947,10 +20017,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20050,10 +20120,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20151,10 +20221,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20181,7 +20251,7 @@
       </c>
       <c r="L184" s="2"/>
       <c r="M184" t="s" s="2">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -20190,7 +20260,7 @@
       </c>
       <c r="Q184" s="2"/>
       <c r="R184" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="S184" t="s" s="2">
         <v>74</v>
@@ -20232,7 +20302,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -20252,10 +20322,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20289,7 +20359,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>74</v>
@@ -20331,7 +20401,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -20351,10 +20421,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20377,7 +20447,7 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -20430,7 +20500,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-exposition-aux-radiations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
